--- a/outputs/experiment_summary.xlsx
+++ b/outputs/experiment_summary.xlsx
@@ -1,32 +1,227 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Training - Masai - BA with Gen AI\Capstone_Project\adhikkadam_2511363_part2_kpi_experiment\outputs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9139055-EC46-41C8-9DA9-53B915192DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Overall Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Conversion by Region" sheetId="2" r:id="rId2"/>
+    <sheet name="Trial Rate by Device" sheetId="3" r:id="rId3"/>
+    <sheet name="ARPU by Traffic Source" sheetId="4" r:id="rId4"/>
+    <sheet name="Segment_Plan" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="57">
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Required Calculation</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Treatment</t>
+  </si>
+  <si>
+    <t>User count</t>
+  </si>
+  <si>
+    <t>Landing page visit rate</t>
+  </si>
+  <si>
+    <t>Trial start rate</t>
+  </si>
+  <si>
+    <t>Onboarding completion rate</t>
+  </si>
+  <si>
+    <t>Paid conversion rate</t>
+  </si>
+  <si>
+    <t>Average revenue per user</t>
+  </si>
+  <si>
+    <t>Average revenue per converted user</t>
+  </si>
+  <si>
+    <t>Refund rate</t>
+  </si>
+  <si>
+    <t>Support ticket rate</t>
+  </si>
+  <si>
+    <t>Average engagement score</t>
+  </si>
+  <si>
+    <t>Average days to convert</t>
+  </si>
+  <si>
+    <t>Number of users in each group</t>
+  </si>
+  <si>
+    <t>Users who visited landing page / total users</t>
+  </si>
+  <si>
+    <t>Users who started trial / total users</t>
+  </si>
+  <si>
+    <t>Users who completed onboarding / total users</t>
+  </si>
+  <si>
+    <t>Users converted to paid / total users</t>
+  </si>
+  <si>
+    <t>Total revenue / total users</t>
+  </si>
+  <si>
+    <t>Revenue / converted users</t>
+  </si>
+  <si>
+    <t>Refund requests / total users</t>
+  </si>
+  <si>
+    <t>Users with support tickets / total users</t>
+  </si>
+  <si>
+    <t>Average score by group</t>
+  </si>
+  <si>
+    <t>Average days for users who converted</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Tablet</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Organic</t>
+  </si>
+  <si>
+    <t>Paid Search</t>
+  </si>
+  <si>
+    <t>Referral</t>
+  </si>
+  <si>
+    <t>Social</t>
+  </si>
+  <si>
+    <t>Absolute Diff (T-C)</t>
+  </si>
+  <si>
+    <t>Relative Diff (%)</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>User_Count (Control)</t>
+  </si>
+  <si>
+    <t>User_Count (Treatment)</t>
+  </si>
+  <si>
+    <t>Paid_Conversion_Rate (Control)</t>
+  </si>
+  <si>
+    <t>Paid_Conversion_Rate (Treatment)</t>
+  </si>
+  <si>
+    <t>Onboarding_Completion_Rate (Control)</t>
+  </si>
+  <si>
+    <t>Onboarding_Completion_Rate (Treatment)</t>
+  </si>
+  <si>
+    <t>Avg_Engagement_Score (Control)</t>
+  </si>
+  <si>
+    <t>Avg_Engagement_Score (Treatment)</t>
+  </si>
+  <si>
+    <t>Conversion Diff (Absolute)</t>
+  </si>
+  <si>
+    <t>device_type</t>
+  </si>
+  <si>
+    <t>traffic_source</t>
+  </si>
+  <si>
+    <t>plan_type</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>Premium</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +232,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,18 +240,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -69,9 +286,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -79,44 +296,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -146,12 +363,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -181,7 +398,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -190,150 +407,1180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2">
+        <v>687</v>
+      </c>
+      <c r="D2" s="2">
+        <v>710</v>
+      </c>
+      <c r="E2" s="2">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2.8985507246376812</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.63464337700145557</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.72394366197183102</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8.7711777913859978E-2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>13.786133658442679</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.24745269286753999</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.29014084507042248</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3.9416207389263103E-2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>15.720915085891059</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.15283842794759819</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.21126760563380281</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5.4745866503368018E-2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>34.976525821596233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2.7656477438136831E-2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>7.0422535211267609E-2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3.8538477240253118E-2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>120.87067861715749</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="2">
+        <v>24.126098981077149</v>
+      </c>
+      <c r="D7" s="2">
+        <v>54.254521126760572</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4.1547772137170682</v>
+      </c>
+      <c r="F7" s="2">
+        <v>8.2930108803118454</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2">
+        <v>872.34894736842091</v>
+      </c>
+      <c r="D8" s="2">
+        <v>770.41419999999994</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-800.89595000000054</v>
+      </c>
+      <c r="F8" s="2">
+        <v>-50.969946957957369</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4.2253521126760559E-3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4.2253521126760559E-3</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.148471615720524</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.247887323943662</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.1000612369871402</v>
+      </c>
+      <c r="F10" s="2">
+        <v>67.688483844241915</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2">
+        <v>57.041775836972342</v>
+      </c>
+      <c r="D11" s="2">
+        <v>62.90521126760563</v>
+      </c>
+      <c r="E11" s="2">
+        <v>5.8511532965911357</v>
+      </c>
+      <c r="F11" s="2">
+        <v>10.25545509762641</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2">
+        <v>8.3684210526315788</v>
+      </c>
+      <c r="D12" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="E12" s="2">
+        <v>-2.463636363636363</v>
+      </c>
+      <c r="F12" s="2">
+        <v>-27.794871794871788</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2">
+        <v>157</v>
+      </c>
+      <c r="C2" s="2">
+        <v>170</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2.5477707006369432E-2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>6.4705882352941183E-2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.2038216560509554</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.21176470588235291</v>
+      </c>
+      <c r="H2" s="2">
+        <v>56.556050955414008</v>
+      </c>
+      <c r="I2" s="2">
+        <v>63.287352941176472</v>
+      </c>
+      <c r="J2" s="2">
+        <v>3.9228175346571748E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2">
+        <v>201</v>
+      </c>
+      <c r="C3" s="2">
+        <v>180</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3.482587064676617E-2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8.8888888888888892E-2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.13930348258706471</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.2388888888888889</v>
+      </c>
+      <c r="H3" s="2">
+        <v>57.65</v>
+      </c>
+      <c r="I3" s="2">
+        <v>63.080555555555563</v>
+      </c>
+      <c r="J3" s="2">
+        <v>5.4063018242122722E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="2">
+        <v>184</v>
+      </c>
+      <c r="C4" s="2">
+        <v>183</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3.2608695652173912E-2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>7.650273224043716E-2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.13043478260869559</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.21857923497267759</v>
+      </c>
+      <c r="H4" s="2">
+        <v>56.952989130434787</v>
+      </c>
+      <c r="I4" s="2">
+        <v>62.088524590163942</v>
+      </c>
+      <c r="J4" s="2">
+        <v>4.3894036588263248E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="2">
+        <v>148</v>
+      </c>
+      <c r="C5" s="2">
+        <v>177</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3.3783783783783793E-2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5.0847457627118647E-2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.1751412429378531</v>
+      </c>
+      <c r="H5" s="2">
+        <v>56.898648648648653</v>
+      </c>
+      <c r="I5" s="2">
+        <v>63.204237288135587</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.7063673843334862E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="2">
+        <v>200</v>
+      </c>
+      <c r="C2" s="2">
+        <v>213</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>6.5727699530516437E-2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.18779342723004691</v>
+      </c>
+      <c r="H2" s="2">
+        <v>57.225749999999998</v>
+      </c>
+      <c r="I2" s="2">
+        <v>63.178873239436619</v>
+      </c>
+      <c r="J2" s="2">
+        <v>2.0727699530516439E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="2">
+        <v>426</v>
+      </c>
+      <c r="C3" s="2">
+        <v>432</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2.582159624413146E-2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>7.407407407407407E-2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.1384976525821596</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="H3" s="2">
+        <v>57.387323943661968</v>
+      </c>
+      <c r="I3" s="2">
+        <v>62.772453703703697</v>
+      </c>
+      <c r="J3" s="2">
+        <v>4.8252477829942617E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2">
+        <v>55</v>
+      </c>
+      <c r="C4" s="2">
+        <v>56</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1.8181818181818181E-2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.23214285714285721</v>
+      </c>
+      <c r="H4" s="2">
+        <v>55.739090909090912</v>
+      </c>
+      <c r="I4" s="2">
+        <v>63.00714285714286</v>
+      </c>
+      <c r="J4" s="2">
+        <v>5.3246753246753237E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="2">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="H5" s="2">
+        <v>45.5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>62.166666666666657</v>
+      </c>
+      <c r="J5" s="2">
+        <v>-0.1111111111111111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2">
+        <v>73</v>
+      </c>
+      <c r="C2" s="2">
+        <v>56</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2.7397260273972601E-2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.19178082191780821</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.1964285714285714</v>
+      </c>
+      <c r="H2" s="2">
+        <v>57.786301369863011</v>
+      </c>
+      <c r="I2" s="2">
+        <v>62.241071428571431</v>
+      </c>
+      <c r="J2" s="2">
+        <v>4.4031311154598823E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="2">
+        <v>246</v>
+      </c>
+      <c r="C3" s="2">
+        <v>237</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2.032520325203252E-2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>6.3291139240506333E-2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.11382113821138209</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.2067510548523207</v>
+      </c>
+      <c r="H3" s="2">
+        <v>58.457113821138208</v>
+      </c>
+      <c r="I3" s="2">
+        <v>61.545569620253161</v>
+      </c>
+      <c r="J3" s="2">
+        <v>4.2965935988473813E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="2">
+        <v>155</v>
+      </c>
+      <c r="C4" s="2">
+        <v>176</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1.2903225806451609E-2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.14772727272727271</v>
+      </c>
+      <c r="H4" s="2">
+        <v>54.694516129032259</v>
+      </c>
+      <c r="I4" s="2">
+        <v>62.795454545454547</v>
+      </c>
+      <c r="J4" s="2">
+        <v>4.9596774193548389E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="2">
+        <v>81</v>
+      </c>
+      <c r="C5" s="2">
+        <v>91</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2.469135802469136E-2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.1098901098901099</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.2967032967032967</v>
+      </c>
+      <c r="H5" s="2">
+        <v>58.390740740740739</v>
+      </c>
+      <c r="I5" s="2">
+        <v>64.154395604395603</v>
+      </c>
+      <c r="J5" s="2">
+        <v>8.5198751865418532E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2">
+        <v>129</v>
+      </c>
+      <c r="C6" s="2">
+        <v>132</v>
+      </c>
+      <c r="D6" s="2">
+        <v>7.7519379844961239E-2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>6.0606060606060608E-2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.23255813953488369</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H6" s="2">
+        <v>55.90736434108527</v>
+      </c>
+      <c r="I6" s="2">
+        <v>63.738257575757579</v>
+      </c>
+      <c r="J6" s="2">
+        <v>-1.6913319238900631E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2">
+        <v>18</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="H7" s="2">
+        <v>58.183333333333337</v>
+      </c>
+      <c r="I7" s="2">
+        <v>71.522222222222226</v>
+      </c>
+      <c r="J7" s="2">
+        <v>-5.5555555555555552E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FC0D4D-B36D-4C6A-8AFD-88C473548BF4}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2">
+        <v>221</v>
+      </c>
+      <c r="C2">
+        <v>232</v>
+      </c>
+      <c r="D2">
+        <v>3.6199095022624438E-2</v>
+      </c>
+      <c r="E2">
+        <v>3.8793103448275863E-2</v>
+      </c>
+      <c r="F2">
+        <v>0.14027149321266971</v>
+      </c>
+      <c r="G2">
+        <v>0.18965517241379309</v>
+      </c>
+      <c r="H2">
+        <v>56.983484162895927</v>
+      </c>
+      <c r="I2">
+        <v>62.968965517241379</v>
+      </c>
+      <c r="J2">
+        <v>2.5940084256514261E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3">
+        <v>360</v>
+      </c>
+      <c r="C3">
+        <v>366</v>
+      </c>
+      <c r="D3">
+        <v>3.0555555555555551E-2</v>
+      </c>
+      <c r="E3">
+        <v>9.2896174863387984E-2</v>
+      </c>
+      <c r="F3">
+        <v>0.15555555555555561</v>
+      </c>
+      <c r="G3">
+        <v>0.2349726775956284</v>
+      </c>
+      <c r="H3">
+        <v>57.293194444444453</v>
+      </c>
+      <c r="I3">
+        <v>62.178415300546447</v>
+      </c>
+      <c r="J3">
+        <v>6.2340619307832433E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4">
+        <v>109</v>
+      </c>
+      <c r="C4">
+        <v>112</v>
+      </c>
+      <c r="D4">
+        <v>2.7522935779816519E-2</v>
+      </c>
+      <c r="E4">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F4">
+        <v>0.19266055045871561</v>
+      </c>
+      <c r="G4">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="H4">
+        <v>56.407339449541283</v>
+      </c>
+      <c r="I4">
+        <v>65.148214285714289</v>
+      </c>
+      <c r="J4">
+        <v>3.4977064220183478E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>